--- a/questionnaire_templates/007_hospital_waste_reduction_practices_survey--questionnaire_templates.xlsx
+++ b/questionnaire_templates/007_hospital_waste_reduction_practices_survey--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -692,8 +692,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -721,12 +721,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'food_waste'}</t>
+          <t>food_waste</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Food Waste'}</t>
+          <t>Food Waste</t>
         </is>
       </c>
     </row>
@@ -738,12 +738,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'liquid_waste'}</t>
+          <t>liquid_waste</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Liquid Waste'}</t>
+          <t>Liquid Waste</t>
         </is>
       </c>
     </row>
@@ -755,12 +755,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'solids_(non-food)'}</t>
+          <t>solids_(non-food)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Solids (non-food)'}</t>
+          <t>Solids (non-food)</t>
         </is>
       </c>
     </row>
@@ -772,12 +772,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -789,12 +789,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'reduce'}</t>
+          <t>reduce</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Reduce'}</t>
+          <t>Reduce</t>
         </is>
       </c>
     </row>
@@ -806,12 +806,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'reuse'}</t>
+          <t>reuse</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Reuse'}</t>
+          <t>Reuse</t>
         </is>
       </c>
     </row>
@@ -823,12 +823,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'recycle'}</t>
+          <t>recycle</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Recycle'}</t>
+          <t>Recycle</t>
         </is>
       </c>
     </row>
@@ -840,12 +840,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
